--- a/input/projections_fertility.xlsx
+++ b/input/projections_fertility.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA310F5A-90D4-4338-9E69-AE4372ECF145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6B63AA-3957-477F-BC8F-F91909839C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="88">
   <si>
     <t/>
   </si>
@@ -701,9 +701,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -735,7 +735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -743,7 +743,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -768,7 +768,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -786,7 +786,7 @@
         <v>67.666666666666671</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -804,7 +804,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -822,7 +822,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -840,7 +840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -858,7 +858,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -876,7 +876,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -894,7 +894,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -912,7 +912,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -930,7 +930,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -948,7 +948,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -966,7 +966,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -984,7 +984,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>54.666666666666664</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>60.000000000000007</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2057,9 +2057,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC6C525-5E56-43D0-8485-7B36B4DC93F6}">
   <dimension ref="A1:BT2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -2502,443 +2502,557 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331DBE6D-1954-4346-8599-CE9CA47D5F47}">
-  <dimension ref="A1:BT2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:CM2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" t="s">
-        <v>31</v>
-      </c>
-      <c r="U1" t="s">
-        <v>32</v>
-      </c>
-      <c r="V1" t="s">
-        <v>33</v>
-      </c>
-      <c r="W1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>77</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>79</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>80</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>81</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>82</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>2011</v>
+      </c>
+      <c r="C1">
+        <v>2012</v>
+      </c>
+      <c r="D1">
+        <v>2013</v>
+      </c>
+      <c r="E1">
+        <v>2014</v>
+      </c>
+      <c r="F1">
+        <v>2015</v>
+      </c>
+      <c r="G1">
+        <v>2016</v>
+      </c>
+      <c r="H1">
+        <v>2017</v>
+      </c>
+      <c r="I1">
+        <v>2018</v>
+      </c>
+      <c r="J1">
+        <v>2019</v>
+      </c>
+      <c r="K1">
+        <v>2020</v>
+      </c>
+      <c r="L1">
+        <v>2021</v>
+      </c>
+      <c r="M1">
+        <v>2022</v>
+      </c>
+      <c r="N1">
+        <v>2023</v>
+      </c>
+      <c r="O1">
+        <v>2024</v>
+      </c>
+      <c r="P1">
+        <v>2025</v>
+      </c>
+      <c r="Q1">
+        <v>2026</v>
+      </c>
+      <c r="R1">
+        <v>2027</v>
+      </c>
+      <c r="S1">
+        <v>2028</v>
+      </c>
+      <c r="T1">
+        <v>2029</v>
+      </c>
+      <c r="U1">
+        <v>2030</v>
+      </c>
+      <c r="V1">
+        <v>2031</v>
+      </c>
+      <c r="W1">
+        <v>2032</v>
+      </c>
+      <c r="X1">
+        <v>2033</v>
+      </c>
+      <c r="Y1">
+        <v>2034</v>
+      </c>
+      <c r="Z1">
+        <v>2035</v>
+      </c>
+      <c r="AA1">
+        <v>2036</v>
+      </c>
+      <c r="AB1">
+        <v>2037</v>
+      </c>
+      <c r="AC1">
+        <v>2038</v>
+      </c>
+      <c r="AD1">
+        <v>2039</v>
+      </c>
+      <c r="AE1">
+        <v>2040</v>
+      </c>
+      <c r="AF1">
+        <v>2041</v>
+      </c>
+      <c r="AG1">
+        <v>2042</v>
+      </c>
+      <c r="AH1">
+        <v>2043</v>
+      </c>
+      <c r="AI1">
+        <v>2044</v>
+      </c>
+      <c r="AJ1">
+        <v>2045</v>
+      </c>
+      <c r="AK1">
+        <v>2046</v>
+      </c>
+      <c r="AL1">
+        <v>2047</v>
+      </c>
+      <c r="AM1">
+        <v>2048</v>
+      </c>
+      <c r="AN1">
+        <v>2049</v>
+      </c>
+      <c r="AO1">
+        <v>2050</v>
+      </c>
+      <c r="AP1">
+        <v>2051</v>
+      </c>
+      <c r="AQ1">
+        <v>2052</v>
+      </c>
+      <c r="AR1">
+        <v>2053</v>
+      </c>
+      <c r="AS1">
+        <v>2054</v>
+      </c>
+      <c r="AT1">
+        <v>2055</v>
+      </c>
+      <c r="AU1">
+        <v>2056</v>
+      </c>
+      <c r="AV1">
+        <v>2057</v>
+      </c>
+      <c r="AW1">
+        <v>2058</v>
+      </c>
+      <c r="AX1">
+        <v>2059</v>
+      </c>
+      <c r="AY1">
+        <v>2060</v>
+      </c>
+      <c r="AZ1">
+        <v>2061</v>
+      </c>
+      <c r="BA1">
+        <v>2062</v>
+      </c>
+      <c r="BB1">
+        <v>2063</v>
+      </c>
+      <c r="BC1">
+        <v>2064</v>
+      </c>
+      <c r="BD1">
+        <v>2065</v>
+      </c>
+      <c r="BE1">
+        <v>2066</v>
+      </c>
+      <c r="BF1">
+        <v>2067</v>
+      </c>
+      <c r="BG1">
+        <v>2068</v>
+      </c>
+      <c r="BH1">
+        <v>2069</v>
+      </c>
+      <c r="BI1">
+        <v>2070</v>
+      </c>
+      <c r="BJ1">
+        <v>2071</v>
+      </c>
+      <c r="BK1">
+        <v>2072</v>
+      </c>
+      <c r="BL1">
+        <v>2073</v>
+      </c>
+      <c r="BM1">
+        <v>2074</v>
+      </c>
+      <c r="BN1">
+        <v>2075</v>
+      </c>
+      <c r="BO1">
+        <v>2076</v>
+      </c>
+      <c r="BP1">
+        <v>2077</v>
+      </c>
+      <c r="BQ1">
+        <v>2078</v>
+      </c>
+      <c r="BR1">
+        <v>2079</v>
+      </c>
+      <c r="BS1">
+        <v>2080</v>
+      </c>
+      <c r="BT1">
+        <v>2081</v>
+      </c>
+      <c r="BU1">
+        <v>2082</v>
+      </c>
+      <c r="BV1">
+        <v>2083</v>
+      </c>
+      <c r="BW1">
+        <v>2084</v>
+      </c>
+      <c r="BX1">
+        <v>2085</v>
+      </c>
+      <c r="BY1">
+        <v>2086</v>
+      </c>
+      <c r="BZ1">
+        <v>2087</v>
+      </c>
+      <c r="CA1">
+        <v>2088</v>
+      </c>
+      <c r="CB1">
+        <v>2089</v>
+      </c>
+      <c r="CC1">
+        <v>2090</v>
+      </c>
+      <c r="CD1">
+        <v>2091</v>
+      </c>
+      <c r="CE1">
+        <v>2092</v>
+      </c>
+      <c r="CF1">
+        <v>2093</v>
+      </c>
+      <c r="CG1">
+        <v>2094</v>
+      </c>
+      <c r="CH1">
+        <v>2095</v>
+      </c>
+      <c r="CI1">
+        <v>2096</v>
+      </c>
+      <c r="CJ1">
+        <v>2097</v>
+      </c>
+      <c r="CK1">
+        <v>2098</v>
+      </c>
+      <c r="CL1">
+        <v>2099</v>
+      </c>
+      <c r="CM1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:91" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>
       <c r="B2">
-        <v>67.666666666666671</v>
+        <v>47.333333333333329</v>
       </c>
       <c r="C2">
-        <v>64</v>
+        <v>47.333333333333329</v>
       </c>
       <c r="D2">
-        <v>60.333333333333336</v>
+        <v>46.333333333333329</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F2">
-        <v>56.333333333333336</v>
+        <v>45.333333333333336</v>
       </c>
       <c r="G2">
-        <v>58.666666666666664</v>
+        <v>45.333333333333336</v>
       </c>
       <c r="H2">
-        <v>62.333333333333336</v>
+        <v>44.666666666666664</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>43.666666666666664</v>
       </c>
       <c r="J2">
-        <v>61.000000000000007</v>
+        <v>42.333333333333336</v>
       </c>
       <c r="K2">
-        <v>59.333333333333336</v>
+        <v>41.333333333333336</v>
       </c>
       <c r="L2">
-        <v>59.000000000000007</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="M2">
-        <v>59.000000000000007</v>
+        <v>41.321000000000005</v>
       </c>
       <c r="N2">
-        <v>59.666666666666664</v>
+        <v>41.497666666666667</v>
       </c>
       <c r="O2">
-        <v>59.333333333333336</v>
+        <v>41.672666666666672</v>
       </c>
       <c r="P2">
-        <v>60.333333333333336</v>
+        <v>41.853999999999992</v>
       </c>
       <c r="Q2">
-        <v>60.666666666666664</v>
+        <v>42.032666666666671</v>
       </c>
       <c r="R2">
-        <v>59.666666666666664</v>
+        <v>42.209000000000003</v>
       </c>
       <c r="S2">
-        <v>61.000000000000007</v>
+        <v>42.382999999999996</v>
       </c>
       <c r="T2">
-        <v>60.666666666666664</v>
+        <v>42.555</v>
       </c>
       <c r="U2">
-        <v>59.666666666666664</v>
+        <v>42.724666666666671</v>
       </c>
       <c r="V2">
-        <v>58.666666666666664</v>
+        <v>42.892000000000003</v>
       </c>
       <c r="W2">
-        <v>58</v>
+        <v>43.05766666666667</v>
       </c>
       <c r="X2">
-        <v>57</v>
+        <v>43.220999999999997</v>
       </c>
       <c r="Y2">
-        <v>57.666666666666664</v>
+        <v>43.382666666666665</v>
       </c>
       <c r="Z2">
-        <v>57.333333333333336</v>
+        <v>43.542333333333339</v>
       </c>
       <c r="AA2">
-        <v>57</v>
+        <v>43.699999999999996</v>
       </c>
       <c r="AB2">
-        <v>56</v>
+        <v>43.856000000000002</v>
       </c>
       <c r="AC2">
-        <v>54.666666666666664</v>
+        <v>44.01</v>
       </c>
       <c r="AD2">
-        <v>54.333333333333329</v>
+        <v>44.162666666666667</v>
       </c>
       <c r="AE2">
-        <v>54.333333333333329</v>
+        <v>44.313333333333333</v>
       </c>
       <c r="AF2">
-        <v>56.666666666666664</v>
+        <v>44.462666666666664</v>
       </c>
       <c r="AG2">
-        <v>58.666666666666664</v>
+        <v>44.610333333333337</v>
       </c>
       <c r="AH2">
-        <v>58.666666666666664</v>
+        <v>44.756666666666668</v>
       </c>
       <c r="AI2">
-        <v>60.666666666666664</v>
+        <v>44.901333333333334</v>
       </c>
       <c r="AJ2">
-        <v>62.333333333333336</v>
+        <v>45.044666666666664</v>
       </c>
       <c r="AK2">
-        <v>63.666666666666664</v>
+        <v>45.186666666666667</v>
       </c>
       <c r="AL2">
-        <v>63</v>
+        <v>45.327333333333335</v>
       </c>
       <c r="AM2">
-        <v>64</v>
+        <v>45.466666666666669</v>
       </c>
       <c r="AN2">
-        <v>63.666666666666664</v>
+        <v>45.60466666666666</v>
       </c>
       <c r="AO2">
-        <v>64</v>
+        <v>45.741666666666667</v>
       </c>
       <c r="AP2">
-        <v>61.000000000000007</v>
+        <v>45.87766666666667</v>
       </c>
       <c r="AQ2">
-        <v>60.666666666666664</v>
+        <v>46.012333333333338</v>
       </c>
       <c r="AR2">
-        <v>60.000000000000007</v>
+        <v>46.146000000000001</v>
       </c>
       <c r="AS2">
-        <v>59.666666666666664</v>
+        <v>46.278333333333329</v>
       </c>
       <c r="AT2">
-        <v>58</v>
+        <v>46.41</v>
       </c>
       <c r="AU2">
-        <v>56</v>
+        <v>46.540666666666667</v>
       </c>
       <c r="AV2">
-        <v>55.333333333333329</v>
+        <v>46.670666666666669</v>
       </c>
       <c r="AW2">
-        <v>55.333333333333329</v>
+        <v>46.799666666666667</v>
       </c>
       <c r="AX2">
-        <v>55</v>
+        <v>46.927666666666667</v>
       </c>
       <c r="AY2">
-        <v>55</v>
+        <v>47.055</v>
       </c>
       <c r="AZ2">
-        <v>55</v>
+        <v>47.181666666666672</v>
       </c>
       <c r="BA2">
-        <v>55.333333333333329</v>
+        <v>47.307666666666663</v>
       </c>
       <c r="BB2">
-        <v>55.666666666666664</v>
+        <v>47.432666666666663</v>
       </c>
       <c r="BC2">
-        <v>55.666666666666664</v>
+        <v>47.557333333333332</v>
       </c>
       <c r="BD2">
-        <v>56</v>
+        <v>47.681333333333335</v>
       </c>
       <c r="BE2">
-        <v>56.333333333333336</v>
+        <v>47.80466666666667</v>
       </c>
       <c r="BF2">
-        <v>56.666666666666664</v>
+        <v>47.927666666666667</v>
       </c>
       <c r="BG2">
-        <v>56.666666666666664</v>
+        <v>48.050000000000004</v>
       </c>
       <c r="BH2">
-        <v>57</v>
+        <v>48.171999999999997</v>
       </c>
       <c r="BI2">
-        <v>57.333333333333336</v>
+        <v>48.293666666666667</v>
       </c>
       <c r="BJ2">
-        <v>57.666666666666664</v>
+        <v>48.414666666666669</v>
       </c>
       <c r="BK2">
-        <v>58</v>
+        <v>48.535666666666664</v>
       </c>
       <c r="BL2">
-        <v>58.333333333333336</v>
+        <v>48.656000000000006</v>
       </c>
       <c r="BM2">
-        <v>58.333333333333336</v>
+        <v>48.776333333333334</v>
       </c>
       <c r="BN2">
-        <v>58.666666666666664</v>
+        <v>48.896333333333331</v>
       </c>
       <c r="BO2">
-        <v>59.000000000000007</v>
+        <v>49.015999999999998</v>
       </c>
       <c r="BP2">
-        <v>59.000000000000007</v>
+        <v>49.135333333333328</v>
       </c>
       <c r="BQ2">
-        <v>59.333333333333336</v>
+        <v>49.254666666666665</v>
       </c>
       <c r="BR2">
-        <v>59.333333333333336</v>
+        <v>49.374000000000002</v>
       </c>
       <c r="BS2">
-        <v>59.333333333333336</v>
+        <v>49.493000000000002</v>
       </c>
       <c r="BT2">
-        <v>59.333333333333336</v>
+        <v>49.612333333333332</v>
+      </c>
+      <c r="BU2">
+        <v>49.730999999999995</v>
+      </c>
+      <c r="BV2">
+        <v>49.85</v>
+      </c>
+      <c r="BW2">
+        <v>49.969000000000001</v>
+      </c>
+      <c r="BX2">
+        <v>50.088000000000001</v>
+      </c>
+      <c r="BY2">
+        <v>50.207333333333331</v>
+      </c>
+      <c r="BZ2">
+        <v>50.326333333333331</v>
+      </c>
+      <c r="CA2">
+        <v>50.445666666666675</v>
+      </c>
+      <c r="CB2">
+        <v>50.564999999999998</v>
+      </c>
+      <c r="CC2">
+        <v>50.684666666666672</v>
+      </c>
+      <c r="CD2">
+        <v>50.80466666666667</v>
+      </c>
+      <c r="CE2">
+        <v>50.924666666666667</v>
+      </c>
+      <c r="CF2">
+        <v>51.045000000000002</v>
+      </c>
+      <c r="CG2">
+        <v>51.165666666666667</v>
+      </c>
+      <c r="CH2">
+        <v>51.286333333333332</v>
+      </c>
+      <c r="CI2">
+        <v>51.407666666666664</v>
+      </c>
+      <c r="CJ2">
+        <v>51.529000000000003</v>
+      </c>
+      <c r="CK2">
+        <v>51.651000000000003</v>
+      </c>
+      <c r="CL2">
+        <v>51.773333333333333</v>
+      </c>
+      <c r="CM2">
+        <v>51.896000000000008</v>
       </c>
     </row>
   </sheetData>
@@ -2949,9 +3063,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F67E40-71C1-4822-9F58-EAF4B2A32D1B}">
   <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -3061,7 +3175,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>

--- a/input/projections_fertility.xlsx
+++ b/input/projections_fertility.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6B63AA-3957-477F-BC8F-F91909839C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C4FE87-92D9-43DD-8271-B845110E7C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="UK_FertilityByYear" sheetId="3" r:id="rId2"/>
     <sheet name="IT_FertilityByYear" sheetId="4" r:id="rId3"/>
     <sheet name="PL_FertilityByYear" sheetId="5" r:id="rId4"/>
+    <sheet name="EL_FertilityByYear" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="88">
   <si>
     <t/>
   </si>
@@ -701,9 +702,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -711,7 +712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -719,7 +720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -727,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -735,7 +736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -743,7 +744,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -751,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -768,7 +769,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -786,7 +787,7 @@
         <v>67.666666666666671</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -804,7 +805,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -822,7 +823,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -840,7 +841,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -858,7 +859,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -876,7 +877,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -894,7 +895,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -912,7 +913,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -930,7 +931,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -948,7 +949,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -966,7 +967,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -984,7 +985,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1002,7 +1003,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1075,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1110,7 +1111,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1146,7 +1147,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1164,7 +1165,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1182,7 +1183,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1236,7 +1237,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1272,7 +1273,7 @@
         <v>54.666666666666664</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1308,7 +1309,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1326,7 +1327,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1362,7 +1363,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1398,7 +1399,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1434,7 +1435,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1452,7 +1453,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1488,7 +1489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1506,7 +1507,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1524,7 +1525,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1542,7 +1543,7 @@
         <v>60.000000000000007</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1560,7 +1561,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1578,7 +1579,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1596,7 +1597,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1650,7 +1651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -1686,7 +1687,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -1722,7 +1723,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -1740,7 +1741,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -1758,7 +1759,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1776,7 +1777,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -1812,7 +1813,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -1830,7 +1831,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -1866,7 +1867,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -1884,7 +1885,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -1902,7 +1903,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -1920,7 +1921,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -1974,7 +1975,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2057,9 +2058,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC6C525-5E56-43D0-8485-7B36B4DC93F6}">
   <dimension ref="A1:BT2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2277,7 +2278,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -2503,9 +2504,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331DBE6D-1954-4346-8599-CE9CA47D5F47}">
   <dimension ref="A1:CM2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -3063,9 +3064,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F67E40-71C1-4822-9F58-EAF4B2A32D1B}">
   <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -3283,6 +3284,566 @@
       </c>
       <c r="AJ2" s="3">
         <v>50.862424293074902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E31A1416-D081-438C-9182-88E649DA964C}">
+  <dimension ref="A1:CM2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1">
+        <v>2011</v>
+      </c>
+      <c r="C1">
+        <v>2012</v>
+      </c>
+      <c r="D1">
+        <v>2013</v>
+      </c>
+      <c r="E1">
+        <v>2014</v>
+      </c>
+      <c r="F1">
+        <v>2015</v>
+      </c>
+      <c r="G1">
+        <v>2016</v>
+      </c>
+      <c r="H1">
+        <v>2017</v>
+      </c>
+      <c r="I1">
+        <v>2018</v>
+      </c>
+      <c r="J1">
+        <v>2019</v>
+      </c>
+      <c r="K1">
+        <v>2020</v>
+      </c>
+      <c r="L1">
+        <v>2021</v>
+      </c>
+      <c r="M1">
+        <v>2022</v>
+      </c>
+      <c r="N1">
+        <v>2023</v>
+      </c>
+      <c r="O1">
+        <v>2024</v>
+      </c>
+      <c r="P1">
+        <v>2025</v>
+      </c>
+      <c r="Q1">
+        <v>2026</v>
+      </c>
+      <c r="R1">
+        <v>2027</v>
+      </c>
+      <c r="S1">
+        <v>2028</v>
+      </c>
+      <c r="T1">
+        <v>2029</v>
+      </c>
+      <c r="U1">
+        <v>2030</v>
+      </c>
+      <c r="V1">
+        <v>2031</v>
+      </c>
+      <c r="W1">
+        <v>2032</v>
+      </c>
+      <c r="X1">
+        <v>2033</v>
+      </c>
+      <c r="Y1">
+        <v>2034</v>
+      </c>
+      <c r="Z1">
+        <v>2035</v>
+      </c>
+      <c r="AA1">
+        <v>2036</v>
+      </c>
+      <c r="AB1">
+        <v>2037</v>
+      </c>
+      <c r="AC1">
+        <v>2038</v>
+      </c>
+      <c r="AD1">
+        <v>2039</v>
+      </c>
+      <c r="AE1">
+        <v>2040</v>
+      </c>
+      <c r="AF1">
+        <v>2041</v>
+      </c>
+      <c r="AG1">
+        <v>2042</v>
+      </c>
+      <c r="AH1">
+        <v>2043</v>
+      </c>
+      <c r="AI1">
+        <v>2044</v>
+      </c>
+      <c r="AJ1">
+        <v>2045</v>
+      </c>
+      <c r="AK1">
+        <v>2046</v>
+      </c>
+      <c r="AL1">
+        <v>2047</v>
+      </c>
+      <c r="AM1">
+        <v>2048</v>
+      </c>
+      <c r="AN1">
+        <v>2049</v>
+      </c>
+      <c r="AO1">
+        <v>2050</v>
+      </c>
+      <c r="AP1">
+        <v>2051</v>
+      </c>
+      <c r="AQ1">
+        <v>2052</v>
+      </c>
+      <c r="AR1">
+        <v>2053</v>
+      </c>
+      <c r="AS1">
+        <v>2054</v>
+      </c>
+      <c r="AT1">
+        <v>2055</v>
+      </c>
+      <c r="AU1">
+        <v>2056</v>
+      </c>
+      <c r="AV1">
+        <v>2057</v>
+      </c>
+      <c r="AW1">
+        <v>2058</v>
+      </c>
+      <c r="AX1">
+        <v>2059</v>
+      </c>
+      <c r="AY1">
+        <v>2060</v>
+      </c>
+      <c r="AZ1">
+        <v>2061</v>
+      </c>
+      <c r="BA1">
+        <v>2062</v>
+      </c>
+      <c r="BB1">
+        <v>2063</v>
+      </c>
+      <c r="BC1">
+        <v>2064</v>
+      </c>
+      <c r="BD1">
+        <v>2065</v>
+      </c>
+      <c r="BE1">
+        <v>2066</v>
+      </c>
+      <c r="BF1">
+        <v>2067</v>
+      </c>
+      <c r="BG1">
+        <v>2068</v>
+      </c>
+      <c r="BH1">
+        <v>2069</v>
+      </c>
+      <c r="BI1">
+        <v>2070</v>
+      </c>
+      <c r="BJ1">
+        <v>2071</v>
+      </c>
+      <c r="BK1">
+        <v>2072</v>
+      </c>
+      <c r="BL1">
+        <v>2073</v>
+      </c>
+      <c r="BM1">
+        <v>2074</v>
+      </c>
+      <c r="BN1">
+        <v>2075</v>
+      </c>
+      <c r="BO1">
+        <v>2076</v>
+      </c>
+      <c r="BP1">
+        <v>2077</v>
+      </c>
+      <c r="BQ1">
+        <v>2078</v>
+      </c>
+      <c r="BR1">
+        <v>2079</v>
+      </c>
+      <c r="BS1">
+        <v>2080</v>
+      </c>
+      <c r="BT1">
+        <v>2081</v>
+      </c>
+      <c r="BU1">
+        <v>2082</v>
+      </c>
+      <c r="BV1">
+        <v>2083</v>
+      </c>
+      <c r="BW1">
+        <v>2084</v>
+      </c>
+      <c r="BX1">
+        <v>2085</v>
+      </c>
+      <c r="BY1">
+        <v>2086</v>
+      </c>
+      <c r="BZ1">
+        <v>2087</v>
+      </c>
+      <c r="CA1">
+        <v>2088</v>
+      </c>
+      <c r="CB1">
+        <v>2089</v>
+      </c>
+      <c r="CC1">
+        <v>2090</v>
+      </c>
+      <c r="CD1">
+        <v>2091</v>
+      </c>
+      <c r="CE1">
+        <v>2092</v>
+      </c>
+      <c r="CF1">
+        <v>2093</v>
+      </c>
+      <c r="CG1">
+        <v>2094</v>
+      </c>
+      <c r="CH1">
+        <v>2095</v>
+      </c>
+      <c r="CI1">
+        <v>2096</v>
+      </c>
+      <c r="CJ1">
+        <v>2097</v>
+      </c>
+      <c r="CK1">
+        <v>2098</v>
+      </c>
+      <c r="CL1">
+        <v>2099</v>
+      </c>
+      <c r="CM1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2">
+        <v>44.666666666666664</v>
+      </c>
+      <c r="C2">
+        <v>44.666666666666664</v>
+      </c>
+      <c r="D2">
+        <v>43</v>
+      </c>
+      <c r="E2">
+        <v>43.333333333333336</v>
+      </c>
+      <c r="F2">
+        <v>44.333333333333336</v>
+      </c>
+      <c r="G2">
+        <v>46</v>
+      </c>
+      <c r="H2">
+        <v>45.000000000000007</v>
+      </c>
+      <c r="I2">
+        <v>45.000000000000007</v>
+      </c>
+      <c r="J2">
+        <v>44.666666666666664</v>
+      </c>
+      <c r="K2">
+        <v>46.333333333333329</v>
+      </c>
+      <c r="L2">
+        <v>47.666666666666664</v>
+      </c>
+      <c r="M2">
+        <v>44.000000000000007</v>
+      </c>
+      <c r="N2">
+        <v>42</v>
+      </c>
+      <c r="O2">
+        <v>47.17</v>
+      </c>
+      <c r="P2">
+        <v>47.300000000000004</v>
+      </c>
+      <c r="Q2">
+        <v>47.427666666666667</v>
+      </c>
+      <c r="R2">
+        <v>47.552999999999997</v>
+      </c>
+      <c r="S2">
+        <v>47.676333333333332</v>
+      </c>
+      <c r="T2">
+        <v>47.797666666666665</v>
+      </c>
+      <c r="U2">
+        <v>47.916666666666671</v>
+      </c>
+      <c r="V2">
+        <v>48.033999999999999</v>
+      </c>
+      <c r="W2">
+        <v>48.149333333333338</v>
+      </c>
+      <c r="X2">
+        <v>48.262666666666668</v>
+      </c>
+      <c r="Y2">
+        <v>48.374333333333333</v>
+      </c>
+      <c r="Z2">
+        <v>48.484333333333339</v>
+      </c>
+      <c r="AA2">
+        <v>48.592666666666666</v>
+      </c>
+      <c r="AB2">
+        <v>48.699000000000005</v>
+      </c>
+      <c r="AC2">
+        <v>48.804000000000002</v>
+      </c>
+      <c r="AD2">
+        <v>48.907666666666671</v>
+      </c>
+      <c r="AE2">
+        <v>49.009666666666668</v>
+      </c>
+      <c r="AF2">
+        <v>49.11</v>
+      </c>
+      <c r="AG2">
+        <v>49.209333333333333</v>
+      </c>
+      <c r="AH2">
+        <v>49.306999999999995</v>
+      </c>
+      <c r="AI2">
+        <v>49.403666666666666</v>
+      </c>
+      <c r="AJ2">
+        <v>49.498999999999995</v>
+      </c>
+      <c r="AK2">
+        <v>49.592999999999996</v>
+      </c>
+      <c r="AL2">
+        <v>49.685666666666663</v>
+      </c>
+      <c r="AM2">
+        <v>49.777666666666669</v>
+      </c>
+      <c r="AN2">
+        <v>49.868333333333332</v>
+      </c>
+      <c r="AO2">
+        <v>49.957999999999998</v>
+      </c>
+      <c r="AP2">
+        <v>50.046666666666667</v>
+      </c>
+      <c r="AQ2">
+        <v>50.134666666666668</v>
+      </c>
+      <c r="AR2">
+        <v>50.221333333333334</v>
+      </c>
+      <c r="AS2">
+        <v>50.30766666666667</v>
+      </c>
+      <c r="AT2">
+        <v>50.392666666666663</v>
+      </c>
+      <c r="AU2">
+        <v>50.477333333333341</v>
+      </c>
+      <c r="AV2">
+        <v>50.560999999999993</v>
+      </c>
+      <c r="AW2">
+        <v>50.643999999999998</v>
+      </c>
+      <c r="AX2">
+        <v>50.726333333333329</v>
+      </c>
+      <c r="AY2">
+        <v>50.808</v>
+      </c>
+      <c r="AZ2">
+        <v>50.888999999999996</v>
+      </c>
+      <c r="BA2">
+        <v>50.969666666666669</v>
+      </c>
+      <c r="BB2">
+        <v>51.049666666666667</v>
+      </c>
+      <c r="BC2">
+        <v>51.129333333333335</v>
+      </c>
+      <c r="BD2">
+        <v>51.208333333333329</v>
+      </c>
+      <c r="BE2">
+        <v>51.287333333333336</v>
+      </c>
+      <c r="BF2">
+        <v>51.365666666666662</v>
+      </c>
+      <c r="BG2">
+        <v>51.443666666666665</v>
+      </c>
+      <c r="BH2">
+        <v>51.521333333333331</v>
+      </c>
+      <c r="BI2">
+        <v>51.598666666666666</v>
+      </c>
+      <c r="BJ2">
+        <v>51.675666666666672</v>
+      </c>
+      <c r="BK2">
+        <v>51.75266666666667</v>
+      </c>
+      <c r="BL2">
+        <v>51.829333333333331</v>
+      </c>
+      <c r="BM2">
+        <v>51.905999999999999</v>
+      </c>
+      <c r="BN2">
+        <v>51.98266666666666</v>
+      </c>
+      <c r="BO2">
+        <v>52.059000000000005</v>
+      </c>
+      <c r="BP2">
+        <v>52.135333333333335</v>
+      </c>
+      <c r="BQ2">
+        <v>52.211333333333336</v>
+      </c>
+      <c r="BR2">
+        <v>52.287666666666659</v>
+      </c>
+      <c r="BS2">
+        <v>52.364000000000004</v>
+      </c>
+      <c r="BT2">
+        <v>52.440333333333335</v>
+      </c>
+      <c r="BU2">
+        <v>52.516666666666666</v>
+      </c>
+      <c r="BV2">
+        <v>52.593000000000004</v>
+      </c>
+      <c r="BW2">
+        <v>52.669666666666664</v>
+      </c>
+      <c r="BX2">
+        <v>52.746333333333332</v>
+      </c>
+      <c r="BY2">
+        <v>52.822999999999993</v>
+      </c>
+      <c r="BZ2">
+        <v>52.900333333333336</v>
+      </c>
+      <c r="CA2">
+        <v>52.977666666666664</v>
+      </c>
+      <c r="CB2">
+        <v>53.055</v>
+      </c>
+      <c r="CC2">
+        <v>53.133000000000003</v>
+      </c>
+      <c r="CD2">
+        <v>53.210999999999999</v>
+      </c>
+      <c r="CE2">
+        <v>53.289333333333332</v>
+      </c>
+      <c r="CF2">
+        <v>53.368000000000002</v>
+      </c>
+      <c r="CG2">
+        <v>53.447333333333333</v>
+      </c>
+      <c r="CH2">
+        <v>53.526666666666657</v>
+      </c>
+      <c r="CI2">
+        <v>53.606666666666669</v>
+      </c>
+      <c r="CJ2">
+        <v>53.687000000000005</v>
+      </c>
+      <c r="CK2">
+        <v>53.767666666666663</v>
+      </c>
+      <c r="CL2">
+        <v>53.849000000000004</v>
+      </c>
+      <c r="CM2">
+        <v>53.930666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/input/projections_fertility.xlsx
+++ b/input/projections_fertility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C4FE87-92D9-43DD-8271-B845110E7C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E6C371-0A58-4D0B-B8DA-F2A57383B141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/input/projections_fertility.xlsx
+++ b/input/projections_fertility.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E268E892-D14D-4480-8A90-D0AA4EA574E7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2AC8B9-4751-8F42-B10D-F30EA2EB9805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1320" windowWidth="31350" windowHeight="16950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1320" windowWidth="30240" windowHeight="16960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_FertilityByYear" sheetId="3" r:id="rId2"/>
-    <sheet name="IT_FertilityByYear" sheetId="4" r:id="rId3"/>
+    <sheet name="FertilityByYear" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
   <si>
     <t/>
   </si>
@@ -402,9 +401,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -442,7 +441,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -548,7 +547,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -690,7 +689,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -699,9 +698,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -709,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -717,7 +716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -725,7 +724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -733,7 +732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -741,7 +740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -749,7 +748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -766,7 +765,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -784,7 +783,7 @@
         <v>67.666666666666671</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -802,7 +801,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -820,7 +819,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -838,7 +837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -856,7 +855,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -874,7 +873,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -892,7 +891,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -910,7 +909,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -928,7 +927,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -946,7 +945,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -964,7 +963,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -982,7 +981,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1000,7 +999,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1018,7 +1017,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1036,7 +1035,7 @@
         <v>60.333333333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1054,7 +1053,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1108,7 +1107,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1125,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1144,7 +1143,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1162,7 +1161,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1180,7 +1179,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1198,7 +1197,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1216,7 +1215,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1270,7 +1269,7 @@
         <v>54.666666666666664</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1288,7 +1287,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1306,7 +1305,7 @@
         <v>54.333333333333329</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1324,7 +1323,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1342,7 +1341,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1360,7 +1359,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1378,7 +1377,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1396,7 +1395,7 @@
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1414,7 +1413,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1432,7 +1431,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>63.666666666666664</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1486,7 +1485,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1504,7 +1503,7 @@
         <v>61.000000000000007</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1522,7 +1521,7 @@
         <v>60.666666666666664</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1540,7 +1539,7 @@
         <v>60.000000000000007</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1558,7 +1557,7 @@
         <v>59.666666666666664</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1576,7 +1575,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1594,7 +1593,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -1630,7 +1629,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -1666,7 +1665,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1683,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1702,7 +1701,7 @@
         <v>55.333333333333329</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -1720,7 +1719,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -1738,7 +1737,7 @@
         <v>55.666666666666664</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -1756,7 +1755,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>56.333333333333336</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -1792,7 +1791,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -1810,7 +1809,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -1828,7 +1827,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -1846,7 +1845,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>57.666666666666664</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -1900,7 +1899,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>58.333333333333336</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>58.666666666666664</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -1954,7 +1953,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>59.000000000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -1990,7 +1989,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>59.333333333333336</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2055,9 +2054,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC6C525-5E56-43D0-8485-7B36B4DC93F6}">
   <dimension ref="A1:BT2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2275,453 +2274,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2">
-        <v>67.666666666666671</v>
-      </c>
-      <c r="C2">
-        <v>64</v>
-      </c>
-      <c r="D2">
-        <v>60.333333333333336</v>
-      </c>
-      <c r="E2">
-        <v>58</v>
-      </c>
-      <c r="F2">
-        <v>56.333333333333336</v>
-      </c>
-      <c r="G2">
-        <v>58.666666666666664</v>
-      </c>
-      <c r="H2">
-        <v>62.333333333333336</v>
-      </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
-      <c r="J2">
-        <v>61.000000000000007</v>
-      </c>
-      <c r="K2">
-        <v>59.333333333333336</v>
-      </c>
-      <c r="L2">
-        <v>59.000000000000007</v>
-      </c>
-      <c r="M2">
-        <v>59.000000000000007</v>
-      </c>
-      <c r="N2">
-        <v>59.666666666666664</v>
-      </c>
-      <c r="O2">
-        <v>59.333333333333336</v>
-      </c>
-      <c r="P2">
-        <v>60.333333333333336</v>
-      </c>
-      <c r="Q2">
-        <v>60.666666666666664</v>
-      </c>
-      <c r="R2">
-        <v>59.666666666666664</v>
-      </c>
-      <c r="S2">
-        <v>61.000000000000007</v>
-      </c>
-      <c r="T2">
-        <v>60.666666666666664</v>
-      </c>
-      <c r="U2">
-        <v>59.666666666666664</v>
-      </c>
-      <c r="V2">
-        <v>58.666666666666664</v>
-      </c>
-      <c r="W2">
-        <v>58</v>
-      </c>
-      <c r="X2">
-        <v>57</v>
-      </c>
-      <c r="Y2">
-        <v>57.666666666666664</v>
-      </c>
-      <c r="Z2">
-        <v>57.333333333333336</v>
-      </c>
-      <c r="AA2">
-        <v>57</v>
-      </c>
-      <c r="AB2">
-        <v>56</v>
-      </c>
-      <c r="AC2">
-        <v>54.666666666666664</v>
-      </c>
-      <c r="AD2">
-        <v>54.333333333333329</v>
-      </c>
-      <c r="AE2">
-        <v>54.333333333333329</v>
-      </c>
-      <c r="AF2">
-        <v>56.666666666666664</v>
-      </c>
-      <c r="AG2">
-        <v>58.666666666666664</v>
-      </c>
-      <c r="AH2">
-        <v>58.666666666666664</v>
-      </c>
-      <c r="AI2">
-        <v>60.666666666666664</v>
-      </c>
-      <c r="AJ2">
-        <v>62.333333333333336</v>
-      </c>
-      <c r="AK2">
-        <v>63.666666666666664</v>
-      </c>
-      <c r="AL2">
-        <v>63</v>
-      </c>
-      <c r="AM2">
-        <v>64</v>
-      </c>
-      <c r="AN2">
-        <v>63.666666666666664</v>
-      </c>
-      <c r="AO2">
-        <v>64</v>
-      </c>
-      <c r="AP2">
-        <v>61.000000000000007</v>
-      </c>
-      <c r="AQ2">
-        <v>60.666666666666664</v>
-      </c>
-      <c r="AR2">
-        <v>60.000000000000007</v>
-      </c>
-      <c r="AS2">
-        <v>59.666666666666664</v>
-      </c>
-      <c r="AT2">
-        <v>58</v>
-      </c>
-      <c r="AU2">
-        <v>56</v>
-      </c>
-      <c r="AV2">
-        <v>55.333333333333329</v>
-      </c>
-      <c r="AW2">
-        <v>55.333333333333329</v>
-      </c>
-      <c r="AX2">
-        <v>55</v>
-      </c>
-      <c r="AY2">
-        <v>55</v>
-      </c>
-      <c r="AZ2">
-        <v>55</v>
-      </c>
-      <c r="BA2">
-        <v>55.333333333333329</v>
-      </c>
-      <c r="BB2">
-        <v>55.666666666666664</v>
-      </c>
-      <c r="BC2">
-        <v>55.666666666666664</v>
-      </c>
-      <c r="BD2">
-        <v>56</v>
-      </c>
-      <c r="BE2">
-        <v>56.333333333333336</v>
-      </c>
-      <c r="BF2">
-        <v>56.666666666666664</v>
-      </c>
-      <c r="BG2">
-        <v>56.666666666666664</v>
-      </c>
-      <c r="BH2">
-        <v>57</v>
-      </c>
-      <c r="BI2">
-        <v>57.333333333333336</v>
-      </c>
-      <c r="BJ2">
-        <v>57.666666666666664</v>
-      </c>
-      <c r="BK2">
-        <v>58</v>
-      </c>
-      <c r="BL2">
-        <v>58.333333333333336</v>
-      </c>
-      <c r="BM2">
-        <v>58.333333333333336</v>
-      </c>
-      <c r="BN2">
-        <v>58.666666666666664</v>
-      </c>
-      <c r="BO2">
-        <v>59.000000000000007</v>
-      </c>
-      <c r="BP2">
-        <v>59.000000000000007</v>
-      </c>
-      <c r="BQ2">
-        <v>59.333333333333336</v>
-      </c>
-      <c r="BR2">
-        <v>59.333333333333336</v>
-      </c>
-      <c r="BS2">
-        <v>59.333333333333336</v>
-      </c>
-      <c r="BT2">
-        <v>59.333333333333336</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331DBE6D-1954-4346-8599-CE9CA47D5F47}">
-  <dimension ref="A1:BT2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" t="s">
-        <v>31</v>
-      </c>
-      <c r="U1" t="s">
-        <v>32</v>
-      </c>
-      <c r="V1" t="s">
-        <v>33</v>
-      </c>
-      <c r="W1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>77</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>79</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>80</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>81</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>82</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>84</v>
       </c>
